--- a/Team-Data/2011-12/4-5-2011-12.xlsx
+++ b/Team-Data/2011-12/4-5-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.556</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
         <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
@@ -873,25 +940,25 @@
         <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
         <v>15.5</v>
       </c>
       <c r="P3" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
         <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T3" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
         <v>23.5</v>
@@ -903,37 +970,37 @@
         <v>7.3</v>
       </c>
       <c r="X3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA3" t="n">
         <v>18.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>11</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -954,13 +1021,13 @@
         <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -978,13 +1045,13 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1136,13 +1203,13 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1169,7 +1236,7 @@
         <v>23</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
         <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.768</v>
+        <v>0.764</v>
       </c>
       <c r="H5" t="n">
         <v>48.1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
         <v>82.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
@@ -1237,46 +1304,46 @@
         <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
       <c r="R5" t="n">
         <v>13.9</v>
       </c>
       <c r="S5" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T5" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U5" t="n">
         <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
         <v>17.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="AB5" t="n">
         <v>96.8</v>
@@ -1285,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,13 +1367,13 @@
         <v>28</v>
       </c>
       <c r="AI5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>9</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>10</v>
-      </c>
       <c r="AK5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,13 +1385,13 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1567,7 @@
         <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
         <v>7</v>
@@ -1512,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1524,7 +1591,7 @@
         <v>25</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
@@ -1688,7 +1755,7 @@
         <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
@@ -1700,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
         <v>9</v>
@@ -1900,13 +1967,13 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,28 +2020,28 @@
         <v>34.6</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
         <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.753</v>
+        <v>0.758</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
@@ -1986,37 +2053,37 @@
         <v>40</v>
       </c>
       <c r="U9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>23</v>
@@ -2025,16 +2092,16 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
       </c>
       <c r="AJ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK9" t="n">
         <v>25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2046,13 +2113,13 @@
         <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2079,10 +2146,10 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2216,7 +2283,7 @@
         <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2255,13 +2322,13 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2410,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2428,7 +2495,7 @@
         <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2690,10 +2757,10 @@
         <v>7.6</v>
       </c>
       <c r="M13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>16.1</v>
@@ -2714,13 +2781,13 @@
         <v>41.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X13" t="n">
         <v>4.7</v>
@@ -2729,7 +2796,7 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA13" t="n">
         <v>21.4</v>
@@ -2738,13 +2805,13 @@
         <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2777,7 +2844,7 @@
         <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2786,25 +2853,25 @@
         <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>22</v>
@@ -2953,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
         <v>10</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
         <v>17</v>
@@ -3150,7 +3217,7 @@
         <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3174,7 +3241,7 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>2</v>
@@ -3326,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3535,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -3669,13 +3736,13 @@
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3869,7 +3936,7 @@
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
@@ -3896,13 +3963,13 @@
         <v>28</v>
       </c>
       <c r="AY19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA19" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4054,7 +4121,7 @@
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.509</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4140,28 +4207,28 @@
         <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M21" t="n">
         <v>22.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.321</v>
+        <v>0.317</v>
       </c>
       <c r="O21" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P21" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R21" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S21" t="n">
         <v>30.8</v>
@@ -4173,43 +4240,43 @@
         <v>19.7</v>
       </c>
       <c r="V21" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W21" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB21" t="n">
         <v>97.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
         <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
@@ -4221,13 +4288,13 @@
         <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4239,7 +4306,7 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS21" t="n">
         <v>15</v>
@@ -4260,13 +4327,13 @@
         <v>24</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB21" t="n">
         <v>13</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
         <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.582</v>
+        <v>0.593</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
@@ -4501,10 +4568,10 @@
         <v>34.3</v>
       </c>
       <c r="J23" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
@@ -4516,10 +4583,10 @@
         <v>0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P23" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q23" t="n">
         <v>0.648</v>
@@ -4528,13 +4595,13 @@
         <v>10.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>15.4</v>
@@ -4543,37 +4610,37 @@
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y23" t="n">
         <v>4.1</v>
       </c>
-      <c r="Y23" t="n">
-        <v>4</v>
-      </c>
       <c r="Z23" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
         <v>28</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>13</v>
@@ -4758,7 +4825,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
@@ -4767,7 +4834,7 @@
         <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
@@ -4809,7 +4876,7 @@
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>16</v>
@@ -4964,7 +5031,7 @@
         <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>20</v>
@@ -4985,7 +5052,7 @@
         <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5152,7 +5219,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J27" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K27" t="n">
         <v>0.432</v>
@@ -5238,16 +5305,16 @@
         <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.31</v>
+        <v>0.311</v>
       </c>
       <c r="O27" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0.748</v>
@@ -5256,7 +5323,7 @@
         <v>13.7</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T27" t="n">
         <v>43.5</v>
@@ -5271,7 +5338,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y27" t="n">
         <v>6.3</v>
@@ -5280,28 +5347,28 @@
         <v>19.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC27" t="n">
         <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5322,7 +5389,7 @@
         <v>28</v>
       </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
         <v>10</v>
@@ -5334,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5343,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5525,7 +5592,7 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
         <v>21</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>24</v>
@@ -5665,7 +5732,7 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5674,7 +5741,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5701,7 +5768,7 @@
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>12</v>
@@ -5716,7 +5783,7 @@
         <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5856,7 +5923,7 @@
         <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.218</v>
+        <v>0.222</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5957,25 +6024,25 @@
         <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L31" t="n">
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N31" t="n">
         <v>0.321</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0.725</v>
@@ -5984,7 +6051,7 @@
         <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T31" t="n">
         <v>41.4</v>
@@ -5999,25 +6066,25 @@
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
         <v>93.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.9</v>
+        <v>-7</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,16 +6096,16 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6050,22 +6117,22 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6080,10 +6147,10 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-5-2011-12</t>
+          <t>2012-04-05</t>
         </is>
       </c>
     </row>
